--- a/data.mn/public/datasets/imported-vehicles-cars-by-country.xlsx
+++ b/data.mn/public/datasets/imported-vehicles-cars-by-country.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mongolian" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,6 +416,11 @@
   </sheetPr>
   <dimension ref="A1:C210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -795,7 +800,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30">
@@ -938,7 +943,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41">
@@ -1081,7 +1086,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52">
@@ -1224,7 +1229,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63">
@@ -1510,7 +1515,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="85">
@@ -1653,7 +1658,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96">
@@ -1796,7 +1801,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="107">
@@ -2082,7 +2087,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="129">
@@ -2225,7 +2230,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="140">
@@ -2368,7 +2373,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="151">
@@ -2654,7 +2659,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>175</v>
+        <v>299</v>
       </c>
     </row>
     <row r="173">
@@ -2797,7 +2802,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>224</v>
+        <v>298</v>
       </c>
     </row>
     <row r="184">
@@ -2940,7 +2945,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>444</v>
+        <v>510</v>
       </c>
     </row>
     <row r="195">
@@ -3031,7 +3036,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="202">
@@ -3044,7 +3049,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>3893</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="203">
@@ -3057,7 +3062,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>913</v>
+        <v>919</v>
       </c>
     </row>
     <row r="204">
@@ -3070,7 +3075,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>82614</v>
+        <v>82811</v>
       </c>
     </row>
     <row r="205">
@@ -3083,7 +3088,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>201</v>
+        <v>302</v>
       </c>
     </row>
     <row r="206">
@@ -3096,7 +3101,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>839</v>
+        <v>848</v>
       </c>
     </row>
     <row r="207">
@@ -3109,7 +3114,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="208">
@@ -3135,7 +3140,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="210">
@@ -3148,7 +3153,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1072</v>
+        <v>1076</v>
       </c>
     </row>
   </sheetData>
@@ -3164,6 +3169,11 @@
   </sheetPr>
   <dimension ref="A1:C210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3543,7 +3553,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30">
@@ -3686,7 +3696,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41">
@@ -3829,7 +3839,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52">
@@ -3972,7 +3982,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63">
@@ -4258,7 +4268,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="85">
@@ -4401,7 +4411,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96">
@@ -4544,7 +4554,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="107">
@@ -4830,7 +4840,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="129">
@@ -4973,7 +4983,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="140">
@@ -5116,7 +5126,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="151">
@@ -5402,7 +5412,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>175</v>
+        <v>299</v>
       </c>
     </row>
     <row r="173">
@@ -5545,7 +5555,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>224</v>
+        <v>298</v>
       </c>
     </row>
     <row r="184">
@@ -5688,7 +5698,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>444</v>
+        <v>510</v>
       </c>
     </row>
     <row r="195">
@@ -5779,7 +5789,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="202">
@@ -5792,7 +5802,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>3893</v>
+        <v>3924</v>
       </c>
     </row>
     <row r="203">
@@ -5805,7 +5815,7 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>913</v>
+        <v>919</v>
       </c>
     </row>
     <row r="204">
@@ -5818,7 +5828,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>82614</v>
+        <v>82811</v>
       </c>
     </row>
     <row r="205">
@@ -5831,7 +5841,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>201</v>
+        <v>302</v>
       </c>
     </row>
     <row r="206">
@@ -5844,7 +5854,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>839</v>
+        <v>848</v>
       </c>
     </row>
     <row r="207">
@@ -5857,7 +5867,7 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="208">
@@ -5883,7 +5893,7 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="210">
@@ -5896,7 +5906,7 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>1072</v>
+        <v>1076</v>
       </c>
     </row>
   </sheetData>
